--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Hsu 1996.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Hsu 1996.xlsx
@@ -2131,7 +2131,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Параметры алгоритма</t>
+          <t>2) Гиперпараметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Hsu 1996.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Hsu 1996.xlsx
@@ -2131,7 +2131,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Гиперпараметры модели</t>
+          <t>2) Параметры модели</t>
         </is>
       </c>
     </row>
